--- a/school_surveys/007_student_motivation_survey--school_surveys.xlsx
+++ b/school_surveys/007_student_motivation_survey--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'school_surveys'}</t>
+          <t>school_surveys</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'School Surveys'}</t>
+          <t>School Surveys</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'student_assessments'}</t>
+          <t>student_assessments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Student Assessments'}</t>
+          <t>Student Assessments</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'007_student_motivation_survey--school_surveys.yaml'}</t>
+          <t>007_student_motivation_survey--school_surveys.yaml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '007_student_motivation_survey--school_surveys.yaml'}</t>
+          <t>007 student motivation survey--school surveys.yaml</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'student_motivation'}</t>
+          <t>student_motivation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'student_motivation'}</t>
+          <t>student motivation</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'student_engagement'}</t>
+          <t>student_engagement</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'student_engagement'}</t>
+          <t>student engagement</t>
         </is>
       </c>
     </row>
